--- a/error_analysis_details.xlsx
+++ b/error_analysis_details.xlsx
@@ -480,10 +480,10 @@
         <v>0.5862000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.008</v>
+        <v>0.5454</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0386</v>
+        <v>0.4928</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -500,7 +500,13 @@
           <t>"http." Look for a closed padlock icon—a sign your information will be encrypted. If you are unsure whether an email request is legitimate, try to verify it by contacting the company directly. Do not use contact information provided on a website connected to the request; instead, check previous statements for contact information. Information about known phishing attacks is also available online from groups such as the Anti- Phishing Working Group &lt;https://apwg.org/&gt;. (See the APWG eCrime Researc</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1. **Verify the sender before acting** – If an email requests sensitive info or urgent action, do not use the contact details in the message. Instead, call or email the company’s known, official address (or use the phone number on their verified website) to confirm the request.  
+2. **Never click links or open attachments from unknown or suspicious emails** – Hover over URLs to see the real destination; look for a closed padlock icon indicating HTTPS encryption. If the link looks off or the attachment is unexpected, treat it as a potential phishing attempt.  
+3. **Report immediately to your IT or security team** – Forward the suspicious email (without opening attachments) to the designated phishing reporting address and document the incident. This allows the organization</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -512,10 +518,10 @@
         <v>0.5841</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5642</v>
+        <v>0.5059</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5401</v>
+        <v>0.4527</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -534,8 +540,8 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1. **Enforce DMARC, DKIM, and SPF on all outbound email domains** – configure these authentication protocols to reject or quarantine messages that fail domain‑based checks, preventing spoofed phishing emails from reaching users.  
-2. **Require multi‑factor authentication (MFA) for all email and critical service logins** – lock down access so that even if a credential is compromised, an attacker</t>
+          <t>1. **Enforce DMARC, DKIM, and SPF for all outgoing mail** – configure these authentication protocols on every domain you control so that receiving servers can reject or quarantine spoofed messages before they reach users.  
+2. **Deploy advanced email filtering with URL rewriting and attachment sandboxing** – use a gateway that rewrites links to a safe‑browse proxy, scans attachments in a sandbox, and blocks known malicious URLs or file types</t>
         </is>
       </c>
     </row>
@@ -549,10 +555,10 @@
         <v>0.6127</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6109</v>
+        <v>0.5014</v>
       </c>
       <c r="D4" t="n">
-        <v>0.819</v>
+        <v>0.7776</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -571,9 +577,9 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1. **Deploy phishing‑resistant MFA (FIDO2/WebAuthn) on all critical accounts** – replace password‑only logins with hardware security keys or biometric factors for every user, device, and service that handles sensitive data.  
-2. **Integrate MFA with risk‑based access controls** – configure your identity platform to elevate or add additional factors when risk signals (e.g., unfamiliar device, location, or anomalous behavior) are detected, ensuring higher protection for high‑value assets.  
-3. **Centralize MFA monitoring and incident response** – route all MFA authentication events to the SOC, analyze logs for patterns of credential‑</t>
+          <t>1. **Deploy FIDO2/WebAuthn‑based, phishing‑resistant MFA** – Replace password‑only or SMS‑based tokens with hardware security keys or platform authenticators that use public‑key cryptography, ensuring attackers cannot reuse stolen credentials.  
+2. **Implement risk‑adaptive MFA** – Combine the FIDO2 layer with contextual signals (device posture, location, time, transaction value) to trigger additional factors only when risk thresholds are exceeded, keeping user experience smooth for low‑risk access.  
+3. **Centralize MFA monitoring and audit** – Feed all MFA events into a SIEM or SOC dashboard, flagging anomalies (e.g., repeated failed attempts, new device registrations) and enforcing automated remediation (e.g., temporary lockout, credential reset) to quickly contain potential phishing compromises.</t>
         </is>
       </c>
     </row>
@@ -587,10 +593,10 @@
         <v>0.47</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4405</v>
+        <v>0.5542</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6637</v>
+        <v>0.6932</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -609,9 +615,9 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1. **Watch the greeting** – Legitimate senders use your real name or a specific title. A generic salutation such as “Dear Valued Customer” or “Sir/Ma’am” is a red flag.  
-2. **Verify the sender’s contact details** – A trustworthy email includes a clear, verifiable signature block (company name, phone number, physical address). If the signature is missing or the contact info looks suspicious, treat the message with caution.  
-3. **Inspect all links before clicking** – Hover over every hyperlink to view the actual URL. If the link’s domain does not match the claimed sender or uses a shortened/obfuscated address, do not click; instead, navigate directly to the official site.</t>
+          <t>1. **Verify the sender’s identity** – Legitimate emails address you by name and include a full, verifiable contact block (e.g., phone number, email address, and company website). If the greeting is generic (“Dear Valued Customer”) or the signature lacks contact details, treat the message with suspicion.  
+2. **Inspect all links before clicking** – Hover over every hyperlink to confirm the displayed URL matches the domain shown in the link text. If the link points to a suspicious or unrelated domain, or if the URL is obfuscated (e.g., “http://bit.ly/…”), do not click and report the email.  
+3. **Stay current on evolving phishing tactics** – Regularly review reputable security advisories or vendor bulletins that detail new phishing schemes. By keeping your knowledge up‑to‑date, you’ll recognize</t>
         </is>
       </c>
     </row>
@@ -625,10 +631,10 @@
         <v>0.5458</v>
       </c>
       <c r="C6" t="n">
-        <v>0.533</v>
+        <v>0.334</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.2743</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -647,9 +653,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1. **Isolate and contain** the compromised accounts immediately—reset all passwords, revoke active sessions, and block any suspicious IP addresses or domains from accessing internal systems.  
-2. **Investigate and preserve evidence**—collect relevant logs (email, authentication, network), identify the phishing vector and any data exfiltration, and preserve all forensic artifacts for further analysis or legal action.  
-3. **Communicate</t>
+          <t>1. **Isolate and remediate compromised accounts** – Immediately disable the</t>
         </is>
       </c>
     </row>
@@ -663,10 +667,10 @@
         <v>0.6634</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7133</v>
+        <v>0.5775</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7245</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -685,9 +689,8 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1. **Run monthly simulated phishing drills** that mirror real-world tactics, then give instant, personalized feedback on each employee’s response to reinforce learning.  
-2. **Teach concrete “red‑flag” checks**—e.g., verify sender domains, hover over URLs, and confirm requests via a separate channel—using short, scenario‑based videos or interactive quizzes.  
-3. **Combine training with technical safeguards**: enable link‑scanning and spam filtering, and require employees to report suspicious emails through a single, easy‑to‑use reporting button.</t>
+          <t>1. **Run monthly simulated phishing tests** and provide instant, personalized feedback on each employee’s response, highlighting what was correct and what led to a mistake.  
+2. **Teach a three‑step verification routine**: (a) verify the sender’s address against a known list, (b) hover over links to confirm the destination URL, and</t>
         </is>
       </c>
     </row>
@@ -701,10 +704,10 @@
         <v>0.3567</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6445</v>
+        <v>0.5691000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4142</v>
+        <v>0.4422</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -723,8 +726,9 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1. **Leverage domain‑name heuristics in a machine‑learning filter** – train the email filter on features such as domain length, hyphen usage, and similarity to known legitimate domains (see Shirazi et al., 2018). This enables rapid flagging of suspicious URLs before the message reaches users.  
-2. **Enforce strict sender‑authentication checks** – require SPF, DKIM, and DMARC alignment for every incoming mail.</t>
+          <t>1. **Integrate domain‑name analytics into the filter pipeline** – Train a lightweight machine‑learning model on the same domain‑name features (e.g., length, use of numerals, similarity to known legitimate domains) that Shirazi et al. found effective, and score every incoming message’s sender address in real time.  
+2. **Enforce strict email‑authentication checks** – Require SPF, DKIM, and DMARC alignment for all accepted mail; automatically quarantine or flag any message that fails these checks, as spoofed sites and phishing emails often bypass authentication.  
+3. **Deploy adaptive sandboxing with user‑feedback loops** – When a message is flagged as suspicious</t>
         </is>
       </c>
     </row>
@@ -738,10 +742,10 @@
         <v>0.5331</v>
       </c>
       <c r="C9" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.4694</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0774</v>
+        <v>0.4419</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -758,7 +762,13 @@
           <t xml:space="preserve">on WIFI. It changes SSID (set service identifier) which is the same as the original network and creates a hotspot Wi-Fi that looks like the original one. When users connect to the Wi-Fi, Attackers snoop their network traffic and pilfer all their personal information like password, account name, and attached files. This type of attack almost becomes successful because public hotspot users are likely to accept incorrectly and unsigned certificates. For attackers, its big advantage is that they do </t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1. **Verify the sender’s identity before clicking any link** – Cross‑check the email address and domain against known contacts or official company records; if the address looks off (extra characters, misspellings, or a different domain), treat the message as a potential spear‑phishing attempt and do not respond or download attachments.  
+2. **Inspect URLs and attachments for hidden malicious content** – Hover over links to reveal the true destination URL; if the URL does not match the claimed site or contains suspicious subdomains, do not click. For attachments, scan them with up‑to‑date antivirus software and only open files from verified senders.  
+3. **Enforce multi‑factor authentication (MFA) and monitor for credential misuse**</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -770,10 +780,10 @@
         <v>0.5507</v>
       </c>
       <c r="C10" t="n">
-        <v>0.646</v>
+        <v>0.6186</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5395</v>
+        <v>0.6574</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -792,7 +802,9 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1. **Deploy MFA and a “trusted‑sender” whitelist for all executive accounts, and run monthly phishing‑simulation tests that require executives to verify suspicious messages via a</t>
+          <t>1. **Deploy executive‑focused phishing simulations and mandatory training** – run monthly, high‑fidelity email tests that mimic current events or industry news, followed by instant debriefs and a short quiz to reinforce recognition of suspicious links or requests for credentials.  
+2. **Enforce multi‑factor authentication (MFA) and advanced email filtering for all executive accounts** – block or quarantine any email containing embedded URLs or attachments that fail domain‑based reputation checks, and require MFA for any login attempt from an unrecognized device or location.  
+3</t>
         </is>
       </c>
     </row>
@@ -806,10 +818,10 @@
         <v>0.5208</v>
       </c>
       <c r="C11" t="n">
-        <v>0.014</v>
+        <v>0.6106</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0166</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -826,7 +838,13 @@
           <t>cisa.gov central@cisa.dhs.gov @CISAgov @CISACyber @cisagov January 12, 2021 THE THREAT AND HOW TO THINK ABOUT IT Email systems are the preferred attack vector for malicious phishing campaigns. Often, by mentioning current events, threat actors carrying out phishing attacks can craft emails that are likely to capture recipients’ attention and lure them to click a link or download a file containing malicious code. Given the recent shift to more telework and remote options, organizations and worker</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1. **Forward the original email unchanged** – Send the suspicious message (including all headers) to the organization’s dedicated phishing‑reporting address (e.g., phish@company.com) or use the built‑in “Report Phish” button in the mail client.  
+2. **Verify the sender independently** – Contact the purported sender through a known, trusted channel (e.g., the company’s official phone number or a previously verified email address) before taking any action.  
+3. **Avoid interacting with the email** – Do not click links, download attachments, or reply until the security team confirms the message is safe.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
